--- a/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
+++ b/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,10 +81,11 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Zählstatus der Behandlungslinie nach EnLiST: geht die Linie in die LoT-Zählung ein
-(`counted`), ist sie außerhalb der Zählung (`not-counted`, z. B. lokoregionale
-Behandlungslinie) oder eine investigationale Studientherapie (`investigational`,
-EnLiST-Notation „iLoT“ — separat notiert statt regulär gezählt).</t>
+    <t>Zählstatus der Behandlungslinie nach EnLiST: `counted` — die Linie liegt auf
+einer EnLiST-Zählachse (eLoT/aLoT/iLoT; Details in der Extension `enlist-lot`);
+`not-counted` — außerhalb jeder LoT-Zählung, z. B. lokoregionale
+Behandlungslinie (Chirurgie, Strahlentherapie, Ablation) oder
+Management-Abschnitt.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -341,7 +342,7 @@
     <t>Zählstatus</t>
   </si>
   <si>
-    <t>Zählstatus nach EnLiST — counted, not-counted oder investigational / iLoT.</t>
+    <t>Zählstatus nach EnLiST — counted oder not-counted.</t>
   </si>
   <si>
     <t>required</t>

--- a/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
+++ b/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
+++ b/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
+++ b/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
+++ b/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
+++ b/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,10 +82,10 @@
   </si>
   <si>
     <t>Zählstatus der Behandlungslinie nach EnLiST: `counted` — die Linie liegt auf
-einer EnLiST-Zählachse (eLoT/aLoT/iLoT; Details in der Extension `enlist-lot`);
-`not-counted` — außerhalb jeder LoT-Zählung, z. B. lokoregionale
-Behandlungslinie (Chirurgie, Strahlentherapie, Ablation) oder
-Management-Abschnitt.</t>
+einer EnLiST-Zählachse (Designation in `enlist-lot` an der führenden Episode
+bzw. Segment-Marker `enlist-line-segment`); `not-counted` — außerhalb jeder
+LoT-Zählung, z. B. lokoregionale Behandlungslinie (Chirurgie, Strahlentherapie,
+Ablation) oder Management-Abschnitt.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
+++ b/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
+++ b/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
+++ b/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
+++ b/1.0.0-ballot/StructureDefinition-enlist-countable.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
